--- a/docs/deliverables/01_要件定義/要件定義書.xlsx
+++ b/docs/deliverables/01_要件定義/要件定義書.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R8f2f83c27d24454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書情報" sheetId="2" r:id="R0bdf881bc93c42e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目的" sheetId="3" r:id="R0cee28e3efee4526"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対象範囲" sheetId="4" r:id="R929c9fe077584af1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者と権限" sheetId="5" r:id="R01fdcdd91b334fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_認証" sheetId="6" r:id="Rd973d28f9518465b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_ホーム・ナビゲーション" sheetId="7" r:id="Raa5dd303ec2b46dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_勤務表" sheetId="8" r:id="R5a5401b9a0a5487d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_過去勤怠・管理者機能" sheetId="9" r:id="R06a02b7b897c419f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_ファイル・外部連携" sheetId="10" r:id="R0eec8eb389b14f84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非機能要件" sheetId="11" r:id="R4c18bc91e6324d20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本番移行条件" sheetId="12" r:id="R83aee5e919934874"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="Rbb62dfed61924b5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書情報" sheetId="2" r:id="Rc1c9394a46664104"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目的" sheetId="3" r:id="Ra2ce8fe930ea477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対象範囲" sheetId="4" r:id="R47fd0cd405984ec9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者と権限" sheetId="5" r:id="Rc4e9e237082c4b03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_認証" sheetId="6" r:id="Ra0f5603f5e434ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_ホーム・ナビゲーション" sheetId="7" r:id="R3cb8f7d1c7a24108"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_勤務表" sheetId="8" r:id="Rf74ff80e43494964"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_過去勤怠・管理者機能" sheetId="9" r:id="R400b5b5b9502423e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_ファイル・外部連携" sheetId="10" r:id="Rfc1e57d09f194234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非機能要件" sheetId="11" r:id="R841dd813e3534571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本番移行条件" sheetId="12" r:id="R090b4370925449e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2748,19 +2748,19 @@
         <x:v>•</x:v>
       </x:c>
       <x:c r="B7" s="24" t="str">
-        <x:v>右上に現在のユーザーIDを大きく表示する。</x:v>
+        <x:v>右上には現在の利用者の氏名と所属部署だけを表示する。</x:v>
       </x:c>
       <x:c r="C7" s="24" t="str">
-        <x:v>右上に現在のユーザーIDを大きく表示する。</x:v>
+        <x:v>右上には現在の利用者の氏名と所属部署だけを表示する。</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>右上に現在のユーザーIDを大きく表示する。</x:v>
+        <x:v>右上には現在の利用者の氏名と所属部署だけを表示する。</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str">
-        <x:v>右上に現在のユーザーIDを大きく表示する。</x:v>
+        <x:v>右上には現在の利用者の氏名と所属部署だけを表示する。</x:v>
       </x:c>
       <x:c r="F7" s="24" t="str">
-        <x:v>右上に現在のユーザーIDを大きく表示する。</x:v>
+        <x:v>右上には現在の利用者の氏名と所属部署だけを表示する。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
